--- a/data/trans_dic/P3A_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,3</t>
+          <t>1,5; 3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,01</t>
+          <t>4,12; 7,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,3</t>
+          <t>3,44; 6,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,99</t>
+          <t>8,5; 12,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,78</t>
+          <t>1,97; 3,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,3</t>
+          <t>5,48; 8,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,48</t>
+          <t>4,31; 7,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,42; 16,04</t>
+          <t>12,12; 15,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,25</t>
+          <t>2,0; 3,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,18</t>
+          <t>5,28; 7,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,46</t>
+          <t>4,26; 6,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 14,14</t>
+          <t>11,24; 13,94</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,14</t>
+          <t>1,65; 3,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,55</t>
+          <t>1,31; 2,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,76</t>
+          <t>0,77; 1,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,94</t>
+          <t>1,48; 3,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,57</t>
+          <t>1,21; 2,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,61</t>
+          <t>1,25; 2,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,91</t>
+          <t>0,76; 1,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,75</t>
+          <t>1,54; 2,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,61</t>
+          <t>1,62; 2,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,32</t>
+          <t>1,42; 2,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,62</t>
+          <t>0,89; 1,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,68</t>
+          <t>1,65; 2,64</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,06</t>
+          <t>10,07; 15,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 11,83</t>
+          <t>6,22; 11,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,16</t>
+          <t>2,44; 6,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,54</t>
+          <t>5,34; 9,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,48</t>
+          <t>6,24; 11,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,15</t>
+          <t>5,43; 11,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,02</t>
+          <t>3,21; 7,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,35</t>
+          <t>5,13; 8,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 13,08</t>
+          <t>8,99; 12,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,38</t>
+          <t>6,43; 10,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,91</t>
+          <t>3,19; 5,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,31</t>
+          <t>5,71; 8,28</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,77</t>
+          <t>3,4; 4,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,51</t>
+          <t>3,22; 4,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,1</t>
+          <t>1,95; 3,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,18</t>
+          <t>3,37; 5,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,81</t>
+          <t>2,55; 3,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,31</t>
+          <t>3,8; 5,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,68</t>
+          <t>2,41; 3,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,16</t>
+          <t>4,35; 6,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,08</t>
+          <t>3,15; 4,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 4,72</t>
+          <t>3,71; 4,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,17</t>
+          <t>2,35; 3,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 5,41</t>
+          <t>4,29; 5,46</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15267; 34069</t>
+          <t>15466; 34204</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39440; 68267</t>
+          <t>40066; 68482</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25473; 47353</t>
+          <t>25848; 49611</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43003; 66873</t>
+          <t>43769; 66469</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26426; 49704</t>
+          <t>25927; 50515</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72975; 110923</t>
+          <t>73247; 111791</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41178; 74237</t>
+          <t>42782; 76326</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93827; 121149</t>
+          <t>91574; 119755</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44496; 76166</t>
+          <t>46804; 76419</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>121566; 165999</t>
+          <t>121954; 167988</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72861; 112627</t>
+          <t>74298; 114402</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>144045; 179666</t>
+          <t>142799; 177149</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27222; 53108</t>
+          <t>27956; 52583</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24954; 50113</t>
+          <t>25684; 51456</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16169; 36399</t>
+          <t>16022; 37303</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32013; 67360</t>
+          <t>33941; 68782</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18838; 40679</t>
+          <t>19255; 40484</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22201; 45818</t>
+          <t>21916; 46075</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14922; 37952</t>
+          <t>15162; 36918</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33213; 61497</t>
+          <t>34412; 60864</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52009; 85478</t>
+          <t>53085; 85427</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52620; 86212</t>
+          <t>52965; 87123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35733; 65678</t>
+          <t>36275; 65931</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76161; 121193</t>
+          <t>74588; 119502</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55209; 88546</t>
+          <t>55544; 86309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29670; 56938</t>
+          <t>29952; 56605</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12858; 33610</t>
+          <t>13314; 34068</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34875; 61706</t>
+          <t>34536; 61157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29537; 54557</t>
+          <t>29675; 54739</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25213; 51133</t>
+          <t>24909; 50569</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16787; 38484</t>
+          <t>17581; 38600</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34653; 55146</t>
+          <t>33871; 54569</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>93180; 134319</t>
+          <t>92337; 132786</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60878; 97539</t>
+          <t>60440; 98701</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34318; 64714</t>
+          <t>34881; 64937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75558; 108586</t>
+          <t>74655; 108267</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>110225; 156128</t>
+          <t>111528; 161196</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>105524; 154015</t>
+          <t>110115; 157243</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66102; 104395</t>
+          <t>65710; 101998</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>115667; 178805</t>
+          <t>116254; 177026</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87566; 128710</t>
+          <t>86206; 126266</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>134918; 188487</t>
+          <t>134866; 187969</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85865; 129826</t>
+          <t>84928; 129463</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>162773; 225027</t>
+          <t>158774; 221497</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>211408; 271328</t>
+          <t>209386; 269777</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>257061; 328754</t>
+          <t>258618; 327645</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>160958; 218364</t>
+          <t>161786; 219145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>294902; 383958</t>
+          <t>305072; 387686</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,32</t>
+          <t>1,45; 3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,03</t>
+          <t>4,13; 6,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,6</t>
+          <t>3,35; 6,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,91</t>
+          <t>7,93; 12,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,84</t>
+          <t>1,94; 3,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,36</t>
+          <t>5,46; 8,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,69</t>
+          <t>4,04; 7,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,12; 15,85</t>
+          <t>12,11; 15,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,26</t>
+          <t>1,91; 3,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,27</t>
+          <t>5,23; 7,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 6,56</t>
+          <t>4,22; 6,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,24; 13,94</t>
+          <t>10,85; 13,78</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,11</t>
+          <t>1,68; 3,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,62</t>
+          <t>1,29; 2,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,8</t>
+          <t>0,76; 1,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,0</t>
+          <t>1,8; 3,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,62</t>
+          <t>1,24; 2,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,86</t>
+          <t>0,76; 1,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,72</t>
+          <t>1,95; 3,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,61</t>
+          <t>1,61; 2,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,34</t>
+          <t>1,42; 2,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,62</t>
+          <t>0,92; 1,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,64</t>
+          <t>2,06; 2,96</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 15,65</t>
+          <t>10,23; 16,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 11,76</t>
+          <t>6,25; 11,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,24</t>
+          <t>2,47; 6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,46</t>
+          <t>5,32; 9,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 11,52</t>
+          <t>6,43; 11,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,03</t>
+          <t>5,37; 10,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,04</t>
+          <t>3,16; 7,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,26</t>
+          <t>5,23; 8,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 12,93</t>
+          <t>9,06; 12,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,5</t>
+          <t>6,53; 10,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,94</t>
+          <t>3,19; 5,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 8,28</t>
+          <t>5,64; 8,33</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,92</t>
+          <t>3,41; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,6</t>
+          <t>3,14; 4,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,03</t>
+          <t>1,94; 3,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,13</t>
+          <t>3,91; 5,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,74</t>
+          <t>2,57; 3,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,29</t>
+          <t>3,78; 5,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,67</t>
+          <t>2,41; 3,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,06</t>
+          <t>5,25; 6,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,06</t>
+          <t>3,18; 4,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,7</t>
+          <t>3,71; 4,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,18</t>
+          <t>2,34; 3,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 5,46</t>
+          <t>4,82; 5,73</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53289</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>106410</t>
+          <t>114178</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>159699</t>
+          <t>170667</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15466; 34204</t>
+          <t>14931; 34256</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40066; 68482</t>
+          <t>40179; 68072</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25848; 49611</t>
+          <t>25199; 46779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43769; 66469</t>
+          <t>45880; 69734</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25927; 50515</t>
+          <t>25466; 50033</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73247; 111791</t>
+          <t>72967; 110967</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42782; 76326</t>
+          <t>40136; 73779</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91574; 119755</t>
+          <t>99508; 128921</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46804; 76419</t>
+          <t>44899; 75500</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>121954; 167988</t>
+          <t>120752; 169203</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74298; 114402</t>
+          <t>73688; 113579</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>142799; 177149</t>
+          <t>152011; 193020</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>54256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47145</t>
+          <t>54043</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>108299</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27956; 52583</t>
+          <t>28362; 53555</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25684; 51456</t>
+          <t>25392; 52020</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16022; 37303</t>
+          <t>15793; 36369</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33941; 68782</t>
+          <t>40108; 73963</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19255; 40484</t>
+          <t>19107; 40403</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21916; 46075</t>
+          <t>21742; 46590</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15162; 36918</t>
+          <t>15131; 37844</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34412; 60864</t>
+          <t>42397; 66886</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53085; 85427</t>
+          <t>52698; 86329</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52965; 87123</t>
+          <t>52665; 87690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36275; 65931</t>
+          <t>37470; 68042</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74588; 119502</t>
+          <t>90638; 130151</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46255</t>
+          <t>49817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>48719</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90041</t>
+          <t>98536</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55544; 86309</t>
+          <t>56391; 90722</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29952; 56605</t>
+          <t>30064; 57654</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13314; 34068</t>
+          <t>13476; 34322</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34536; 61157</t>
+          <t>37846; 67275</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29675; 54739</t>
+          <t>30556; 54297</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24909; 50569</t>
+          <t>24618; 49891</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17581; 38600</t>
+          <t>17300; 39351</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33871; 54569</t>
+          <t>38408; 60788</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>92337; 132786</t>
+          <t>93039; 132667</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60440; 98701</t>
+          <t>61404; 99237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34881; 64937</t>
+          <t>34884; 64337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74655; 108267</t>
+          <t>81599; 120486</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148889</t>
+          <t>160562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>197341</t>
+          <t>216940</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>346230</t>
+          <t>377502</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>111528; 161196</t>
+          <t>111755; 157176</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>110115; 157243</t>
+          <t>107395; 159074</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65710; 101998</t>
+          <t>65498; 104237</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>116254; 177026</t>
+          <t>137555; 188368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86206; 126266</t>
+          <t>86834; 128260</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>134866; 187969</t>
+          <t>134211; 184175</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84928; 129463</t>
+          <t>84962; 132256</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>158774; 221497</t>
+          <t>195511; 241933</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>209386; 269777</t>
+          <t>211271; 270028</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>258618; 327645</t>
+          <t>258910; 327133</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>161786; 219145</t>
+          <t>161484; 220522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>305072; 387686</t>
+          <t>349433; 415073</t>
         </is>
       </c>
     </row>
